--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486729_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486729_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.997</v>
+        <v>2.2537</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1903</v>
+        <v>-0.4785</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8067</v>
+        <v>2.7322</v>
       </c>
       <c r="G2" t="n">
         <v>3.1318</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1046</v>
+        <v>-0.8479</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9095</v>
+        <v>0.2407</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0141</v>
+        <v>-1.0886</v>
       </c>
       <c r="V2" t="n">
         <v>0.1628</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4765</v>
+        <v>1.5261</v>
       </c>
       <c r="E3" t="n">
         <v>1.9401</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4636</v>
+        <v>-0.4139</v>
       </c>
       <c r="G3" t="n">
         <v>1.3055</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2152</v>
+        <v>-0.1655</v>
       </c>
       <c r="T3" t="n">
         <v>0.0275</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2427</v>
+        <v>-0.193</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9931</v>
+        <v>0.9434</v>
       </c>
       <c r="E4" t="n">
         <v>-0.5872000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5803</v>
+        <v>1.5307</v>
       </c>
       <c r="G4" t="n">
         <v>1.9638</v>
@@ -766,13 +766,13 @@
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1984</v>
+        <v>-0.2481</v>
       </c>
       <c r="T4" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0775</v>
+        <v>0.0278</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5804</v>
+        <v>0.6549</v>
       </c>
       <c r="E5" t="n">
         <v>0.4966</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0838</v>
+        <v>0.1583</v>
       </c>
       <c r="G5" t="n">
         <v>1.1446</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3365</v>
+        <v>-0.262</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6138</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3195</v>
+        <v>0.4465</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1171</v>
+        <v>0.0206</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2024</v>
+        <v>0.4259</v>
       </c>
       <c r="G6" t="n">
         <v>4.8818</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2577</v>
+        <v>-1.1307</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1373</v>
+        <v>0.0408</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.395</v>
+        <v>-1.1716</v>
       </c>
       <c r="V6" t="n">
         <v>-0.4084</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4238</v>
+        <v>-0.4183</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1531</v>
+        <v>-0.098</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2707</v>
+        <v>-0.3203</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0775</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2537</v>
+        <v>-0.2482</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2759</v>
+        <v>-0.2207</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0222</v>
+        <v>-0.0275</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2799</v>
+        <v>-1.2551</v>
       </c>
       <c r="E8" t="n">
         <v>-1.9446</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6647</v>
+        <v>0.6895</v>
       </c>
       <c r="G8" t="n">
         <v>0.386</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3144</v>
+        <v>-0.2896</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1355</v>
+        <v>-1.7259</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4742</v>
+        <v>-1.5364</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6613</v>
+        <v>-0.1895</v>
       </c>
       <c r="G9" t="n">
         <v>3.1313</v>
@@ -1156,13 +1156,13 @@
         <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2711</v>
+        <v>-1.8616</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3797</v>
+        <v>-0.4419</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8914</v>
+        <v>-1.4196</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0648</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2023</v>
+        <v>-3.0478</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7026</v>
+        <v>-3.6475</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5003</v>
+        <v>0.5997</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7791</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.844</v>
+        <v>-0.6895</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3311</v>
+        <v>-0.2759</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5129</v>
+        <v>-0.4136</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9022</v>
+        <v>-4.2966</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9735</v>
+        <v>-5.07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0713</v>
+        <v>0.7733</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6033</v>
@@ -1312,13 +1312,13 @@
         <v>2.3169</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0257</v>
+        <v>-1.4201</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0545</v>
+        <v>-0.042</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0801</v>
+        <v>-1.3781</v>
       </c>
       <c r="V11" t="n">
         <v>-0.694</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3945</v>
+        <v>-6.5009</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7215</v>
+        <v>-5.356</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.673</v>
+        <v>-1.1448</v>
       </c>
       <c r="G12" t="n">
         <v>1.2017</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7278</v>
+        <v>-0.8341</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3039</v>
+        <v>0.0615</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4238</v>
+        <v>-0.8956</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6208</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.9717</v>
+        <v>-11.42</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.8126</v>
+        <v>-16.2609</v>
       </c>
       <c r="F13" t="n">
-        <v>4.8409</v>
+        <v>4.841100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>13.6866</v>
@@ -1468,13 +1468,13 @@
         <v>11.5848</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.549100000000001</v>
+        <v>-7.9973</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6584</v>
+        <v>-1.1066</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.8904</v>
+        <v>-6.8907</v>
       </c>
       <c r="V13" t="n">
         <v>-5.5246</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.276300000000001</v>
+        <v>6.7886</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1246</v>
+        <v>3.4356</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1517</v>
+        <v>3.353</v>
       </c>
       <c r="G14" t="n">
         <v>1.3978</v>
@@ -1546,13 +1546,13 @@
         <v>3.0892</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7492</v>
+        <v>2.2615</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2742</v>
+        <v>1.5852</v>
       </c>
       <c r="U14" t="n">
-        <v>0.475</v>
+        <v>0.6763</v>
       </c>
       <c r="V14" t="n">
         <v>0.0401</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.742</v>
+        <v>4.5672</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9731</v>
+        <v>3.4263</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2312</v>
+        <v>1.1409</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8499</v>
+        <v>0.3745</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7241</v>
+        <v>0.5168</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1258</v>
+        <v>-0.1424</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0474</v>
+        <v>1.5135</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.034</v>
+        <v>1.1381</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0814</v>
+        <v>0.3754</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8973</v>
+        <v>-1.139</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6901</v>
+        <v>-0.6212</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2072</v>
+        <v>-0.5178</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5686</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6401</v>
+        <v>0.3996</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0716</v>
+        <v>0.4416</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2461</v>
+        <v>3.7231</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3921</v>
+        <v>-0.4644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.854</v>
+        <v>4.1875</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3745</v>
+        <v>-2.6157</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5168</v>
+        <v>0.9583</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1424</v>
+        <v>-3.5741</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5135</v>
+        <v>-2.5043</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1381</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3754</v>
+        <v>-3.3253</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.139</v>
+        <v>-0.1115</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6212</v>
+        <v>0.1373</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5178</v>
+        <v>-0.2487</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1239</v>
+        <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4799</v>
+        <v>1.4066</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6347</v>
+        <v>0.5925</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1547</v>
+        <v>0.8141</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2277</v>
+        <v>3.1945</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5133</v>
+        <v>2.4128</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0.7818000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0889</v>
+        <v>2.1925</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0849</v>
+        <v>-0.3314</v>
       </c>
       <c r="F17" t="n">
-        <v>4.1738</v>
+        <v>2.5238</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6157</v>
+        <v>1.1858</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9583</v>
+        <v>-0.903</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.5741</v>
+        <v>2.0888</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.5043</v>
+        <v>2.2356</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8211000000000001</v>
+        <v>-1.5917</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.3253</v>
+        <v>3.8274</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1115</v>
+        <v>-1.0498</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1373</v>
+        <v>0.6887</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2487</v>
+        <v>-1.7385</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7377</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7031</v>
+        <v>3.0892</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7724</v>
+        <v>1.0825</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.028</v>
+        <v>0.7234</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8004</v>
+        <v>0.3591</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1945</v>
+        <v>0.6965</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4128</v>
+        <v>0.5712</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.1253</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7321</v>
+        <v>1.8674</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5898</v>
+        <v>0.1761</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1423</v>
+        <v>1.6912</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6233</v>
@@ -1858,13 +1858,13 @@
         <v>2.7031</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2574</v>
+        <v>1.3926</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9853</v>
+        <v>1.5716</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7279</v>
+        <v>-0.1789</v>
       </c>
       <c r="V18" t="n">
         <v>0.3257</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0351</v>
+        <v>1.8391</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0882</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9469</v>
+        <v>1.2338</v>
       </c>
       <c r="G19" t="n">
         <v>0.1084</v>
@@ -1936,13 +1936,13 @@
         <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.007</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5518</v>
+        <v>-0.0347</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2592</v>
+        <v>0.0277</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0163</v>
+        <v>1.6694</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.469</v>
+        <v>1.8013</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4853</v>
+        <v>-0.1319</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1858</v>
+        <v>-1.8499</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.903</v>
+        <v>-0.7241</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0888</v>
+        <v>-1.1258</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2356</v>
+        <v>0.0474</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5917</v>
+        <v>-0.034</v>
       </c>
       <c r="L20" t="n">
-        <v>3.8274</v>
+        <v>0.0814</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0498</v>
+        <v>-1.8973</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6887</v>
+        <v>-0.6901</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7385</v>
+        <v>-1.2072</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0892</v>
+        <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09379999999999999</v>
+        <v>1.496</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4143</v>
+        <v>1.4683</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3205</v>
+        <v>0.0278</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6965</v>
+        <v>0.2856</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3188</v>
+        <v>1.0883</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3001</v>
+        <v>0.3204</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6189</v>
+        <v>0.7679</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2315</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7835</v>
+        <v>-0.0139</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4691</v>
+        <v>0.1514</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3144</v>
+        <v>-0.1654</v>
       </c>
       <c r="V21" t="n">
         <v>0.3683</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4084</v>
+        <v>-0.4829</v>
       </c>
       <c r="E22" t="n">
         <v>-0.0897</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3187</v>
+        <v>-0.3932</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5243</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1159</v>
+        <v>0.0414</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2262</v>
+        <v>0.1518</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8855</v>
+        <v>-1.3725</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.441</v>
+        <v>-2.0273</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5555</v>
+        <v>0.6548</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1998</v>
@@ -2248,13 +2248,13 @@
         <v>0.9654</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0718</v>
+        <v>0.4412</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.138</v>
+        <v>0.2757</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7172</v>
+        <v>-2.3435</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4462</v>
+        <v>-3.1359</v>
       </c>
       <c r="F24" t="n">
-        <v>0.729</v>
+        <v>0.7924</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3295</v>
@@ -2326,13 +2326,13 @@
         <v>1.7377</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.16</v>
+        <v>0.2136</v>
       </c>
       <c r="T24" t="n">
-        <v>0.11</v>
+        <v>0.4203</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.27</v>
+        <v>-0.2066</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.4726</v>
+        <v>-6.186</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.177899999999999</v>
+        <v>-8.557399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7053</v>
+        <v>2.3714</v>
       </c>
       <c r="G25" t="n">
         <v>-6.3791</v>
@@ -2404,13 +2404,13 @@
         <v>2.3169</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4857</v>
+        <v>0.7723</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.1521</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2583</v>
+        <v>0.9244</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.9719</v>
+        <v>13.3507</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.841000000000001</v>
+        <v>-4.841099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>16.8128</v>
+        <v>18.1916</v>
       </c>
       <c r="G26" t="n">
         <v>-13.6866</v>
@@ -2458,7 +2458,7 @@
         <v>-6.4005</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3711</v>
+        <v>-1.371100000000001</v>
       </c>
       <c r="L26" t="n">
         <v>-5.029199999999999</v>
@@ -2467,7 +2467,7 @@
         <v>-7.2862</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6956</v>
+        <v>-0.6956000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-6.5902</v>
@@ -2482,19 +2482,19 @@
         <v>23.1693</v>
       </c>
       <c r="S26" t="n">
-        <v>8.549200000000001</v>
+        <v>9.927999999999997</v>
       </c>
       <c r="T26" t="n">
-        <v>6.8906</v>
+        <v>6.8908</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6582</v>
+        <v>3.0374</v>
       </c>
       <c r="V26" t="n">
         <v>5.5246</v>
       </c>
       <c r="W26" t="n">
-        <v>6.253500000000001</v>
+        <v>6.2535</v>
       </c>
       <c r="X26" t="n">
         <v>-0.7288</v>
